--- a/reports/一级子公司A_现金流量表_2025-12.xlsx
+++ b/reports/一级子公司A_现金流量表_2025-12.xlsx
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>143754000</v>
+        <v>144426155</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>1793220000</v>
+        <v>1792714307</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>2890827</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>36249729</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>1459638</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>18118670</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>723364</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>9060700</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>582789</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>7248967</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>435139</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>5435326</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>290511</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>3625116</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>218265</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>2717312</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>144818</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>1812684</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>364686</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>4528834</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>181632</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>2277333</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>116045</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>1440115</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>368600</v>
+        <v>366898</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>4598000</v>
+        <v>4598433</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>2619000</v>
+        <v>2628859</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>32670000</v>
+        <v>32670335</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>146741600</v>
+        <v>154829626</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>93120000</v>
+        <v>93444618</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>1161600000</v>
+        <v>1161223490</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>964141</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>12084246</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>729927</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>9058291</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>481840</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>6041281</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>364762</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>4529966</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>241290</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>3020025</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>182888</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>2277064</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>15229000</v>
+        <v>15221651</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>189970000</v>
+        <v>189926221</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>7760000</v>
+        <v>7751225</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>96800000</v>
+        <v>96828234</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>3201000</v>
+        <v>3209406</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>39930000</v>
+        <v>39917128</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>119310000</v>
+        <v>122591748</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>27431600</v>
+        <v>32237878</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3093,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>180000</v>
+        <v>179721</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>2160000</v>
+        <v>2159618</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>1500000</v>
+        <v>1502460</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>18000000</v>
+        <v>17994431</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>920000</v>
+        <v>917183</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>11040000</v>
+        <v>11043651</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>1680000</v>
+        <v>1682181</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>14000000</v>
+        <v>13932392</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>168000000</v>
+        <v>168045435</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2000000</v>
+        <v>2009980</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>24000000</v>
+        <v>23995307</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>10000000</v>
+        <v>9953705</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>120000000</v>
+        <v>120012024</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3454,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>380000</v>
+        <v>380219</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>4560000</v>
+        <v>4558737</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>14380000</v>
+        <v>14312611</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-12700000</v>
+        <v>-12630430</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>3500000</v>
+        <v>3517288</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>42000000</v>
+        <v>41989557</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>5500000</v>
+        <v>5524218</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>66000000</v>
+        <v>65995630</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>5500000</v>
+        <v>5481206</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>66000000</v>
+        <v>65997314</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>180000</v>
+        <v>180373</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>2160000</v>
+        <v>2160310</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>9180000</v>
+        <v>9221879</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>4500000</v>
+        <v>4495048</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>54000000</v>
+        <v>54015899</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>4500000</v>
+        <v>4511697</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>54000000</v>
+        <v>53982336</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>720000</v>
+        <v>717245</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>8640000</v>
+        <v>8642814</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>630000</v>
+        <v>626854</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>7560000</v>
+        <v>7561696</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3935,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>90000</v>
+        <v>90433</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>1080000</v>
+        <v>1079855</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>5310000</v>
+        <v>5302726</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>3870000</v>
+        <v>3919153</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>18601600</v>
+        <v>23526601</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>18601600</v>
+        <v>23526601</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
